--- a/inst/extdata/projects/Example/Configurations/ModelParameters.xlsx
+++ b/inst/extdata/projects/Example/Configurations/ModelParameters.xlsx
@@ -8,9 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet, with comma" sheetId="2" r:id="rId2"/>
-    <sheet name="MissingParam" sheetId="3" r:id="rId3"/>
-    <sheet name="Aciclovir" sheetId="4" r:id="rId4"/>
+    <sheet name="Aciclovir" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,100 +427,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Organism|Liver</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EHC continuous fraction</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Container Path</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>foo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Container Path</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
           <t>Aciclovir</t>
         </is>
       </c>
